--- a/Configuracion_Overhaul.xlsx
+++ b/Configuracion_Overhaul.xlsx
@@ -21,46 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="55">
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arimo"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>ID_Intervencion</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Aptos Narrow"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial Unicode MS"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>Tipo_Posicion</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Aptos Narrow"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial Unicode MS"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>Cantidad</t>
-    </r>
+    <t>ID_Intervencion</t>
   </si>
   <si>
     <t>Codigo_Elemento</t>
@@ -93,7 +54,7 @@
     <t>ID_Componente</t>
   </si>
   <si>
-    <t>omponente_Padre</t>
+    <t>Componente_Padre</t>
   </si>
   <si>
     <t>EECA</t>
@@ -229,7 +190,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -243,13 +204,17 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -283,16 +248,21 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -539,13 +509,13 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>1002343.0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -553,13 +523,13 @@
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>1002422.0</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -567,13 +537,13 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>1002424.0</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -581,13 +551,13 @@
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>1002428.0</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
         <v>48.0</v>
       </c>
     </row>
@@ -595,13 +565,13 @@
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>1002435.0</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
         <v>60.0</v>
       </c>
     </row>
@@ -609,13 +579,13 @@
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>1002439.0</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -623,13 +593,13 @@
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>1002442.0</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -637,13 +607,13 @@
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>1002457.0</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -651,13 +621,13 @@
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>1002507.0</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -665,13 +635,13 @@
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>1002513.0</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="C11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
         <v>48.0</v>
       </c>
     </row>
@@ -679,13 +649,13 @@
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>1002634.0</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="C12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -693,13 +663,13 @@
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>1002637.0</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="C13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -707,13 +677,13 @@
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>1002767.0</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -721,13 +691,13 @@
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>1002768.0</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="C15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -735,13 +705,13 @@
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>1002769.0</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="C16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -749,13 +719,13 @@
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>1002770.0</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
+      <c r="C17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -763,13 +733,13 @@
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>1002773.0</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="C18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -777,13 +747,13 @@
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>1002777.0</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="C19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -791,13 +761,13 @@
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>1002779.0</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -805,13 +775,13 @@
       <c r="A21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>1002782.0</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="C21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -819,13 +789,13 @@
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>1002790.0</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="C22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -833,13 +803,13 @@
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>1002807.0</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="C23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="4">
         <v>6.0</v>
       </c>
     </row>
@@ -847,13 +817,13 @@
       <c r="A24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>1002812.0</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="C24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="4">
         <v>3.0</v>
       </c>
     </row>
@@ -861,13 +831,13 @@
       <c r="A25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="4">
         <v>1002813.0</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="C25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -875,13 +845,13 @@
       <c r="A26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="4">
         <v>1002816.0</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="C26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -889,13 +859,13 @@
       <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="4">
         <v>1002837.0</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="C27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
         <v>7.0</v>
       </c>
     </row>
@@ -903,13 +873,13 @@
       <c r="A28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="4">
         <v>1002840.0</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="C28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -917,13 +887,13 @@
       <c r="A29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="4">
         <v>1002847.0</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="C29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -931,13 +901,13 @@
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="4">
         <v>1002852.0</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="C30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -945,13 +915,13 @@
       <c r="A31" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="4">
         <v>1002857.0</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="C31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -959,13 +929,13 @@
       <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="4">
         <v>1003037.0</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="C32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
         <v>18.0</v>
       </c>
     </row>
@@ -973,13 +943,13 @@
       <c r="A33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="4">
         <v>1003039.0</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="C33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -987,13 +957,13 @@
       <c r="A34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="4">
         <v>1003078.0</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="C34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4">
         <v>52.0</v>
       </c>
     </row>
@@ -1001,13 +971,13 @@
       <c r="A35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="4">
         <v>1003131.0</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2">
+      <c r="C35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1015,13 +985,13 @@
       <c r="A36" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="4">
         <v>1003133.0</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2">
+      <c r="C36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1029,13 +999,13 @@
       <c r="A37" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="4">
         <v>1003187.0</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="2">
+      <c r="C37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1043,13 +1013,13 @@
       <c r="A38" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="4">
         <v>1003195.0</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2">
+      <c r="C38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1057,13 +1027,13 @@
       <c r="A39" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="4">
         <v>1007048.0</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2">
+      <c r="C39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1071,13 +1041,13 @@
       <c r="A40" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1085,13 +1055,13 @@
       <c r="A41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="4">
         <v>2.0</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1099,13 +1069,13 @@
       <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="4">
         <v>3.0</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1113,13 +1083,13 @@
       <c r="A43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1127,13 +1097,13 @@
       <c r="A44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="4">
         <v>1002331.0</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="C44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1141,13 +1111,13 @@
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="4">
         <v>1002334.0</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2">
+      <c r="C45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1155,13 +1125,13 @@
       <c r="A46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="4">
         <v>1002340.0</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2">
+      <c r="C46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1169,13 +1139,13 @@
       <c r="A47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="4">
         <v>1002374.0</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
+      <c r="C47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1183,13 +1153,13 @@
       <c r="A48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="4">
         <v>1002375.0</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2">
+      <c r="C48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1197,13 +1167,13 @@
       <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="4">
         <v>1002423.0</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2">
+      <c r="C49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1211,13 +1181,13 @@
       <c r="A50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="4">
         <v>1002426.0</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2">
+      <c r="C50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1225,13 +1195,13 @@
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="4">
         <v>1002435.0</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
+      <c r="C51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4">
         <v>20.0</v>
       </c>
     </row>
@@ -1239,13 +1209,13 @@
       <c r="A52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="4">
         <v>1002465.0</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2">
+      <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="4">
         <v>16.0</v>
       </c>
     </row>
@@ -1253,13 +1223,13 @@
       <c r="A53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="4">
         <v>1002471.0</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2">
+      <c r="C53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="4">
         <v>6.0</v>
       </c>
     </row>
@@ -1267,13 +1237,13 @@
       <c r="A54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="4">
         <v>1002472.0</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="2">
+      <c r="C54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1281,13 +1251,13 @@
       <c r="A55" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="4">
         <v>1002508.0</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2">
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1295,13 +1265,13 @@
       <c r="A56" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="4">
         <v>1002509.0</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2">
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1309,13 +1279,13 @@
       <c r="A57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="4">
         <v>1002514.0</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="C57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="4">
         <v>48.0</v>
       </c>
     </row>
@@ -1323,13 +1293,13 @@
       <c r="A58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="4">
         <v>1002516.0</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="C58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="4">
         <v>10.0</v>
       </c>
     </row>
@@ -1337,13 +1307,13 @@
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="4">
         <v>1002554.0</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="C59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1351,13 +1321,13 @@
       <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="4">
         <v>1002562.0</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1365,13 +1335,13 @@
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="4">
         <v>1002571.0</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1379,13 +1349,13 @@
       <c r="A62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="4">
         <v>1002638.0</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="C62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1393,13 +1363,13 @@
       <c r="A63" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="4">
         <v>1002651.0</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="C63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -1407,13 +1377,13 @@
       <c r="A64" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="4">
         <v>1002667.0</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="C64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="4">
         <v>20.0</v>
       </c>
     </row>
@@ -1421,13 +1391,13 @@
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="4">
         <v>1002679.0</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="C65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="4">
         <v>6.0</v>
       </c>
     </row>
@@ -1435,13 +1405,13 @@
       <c r="A66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="4">
         <v>1002681.0</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="C66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1449,13 +1419,13 @@
       <c r="A67" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="4">
         <v>1002690.0</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="C67" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1463,13 +1433,13 @@
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="4">
         <v>1002694.0</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="C68" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1477,13 +1447,13 @@
       <c r="A69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="4">
         <v>1002703.0</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C69" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="4">
         <v>6.0</v>
       </c>
     </row>
@@ -1491,13 +1461,13 @@
       <c r="A70" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="4">
         <v>1002734.0</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="C70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1505,13 +1475,13 @@
       <c r="A71" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="4">
         <v>1002867.0</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1519,13 +1489,13 @@
       <c r="A72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="4">
         <v>1002869.0</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1533,13 +1503,13 @@
       <c r="A73" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="4">
         <v>1002927.0</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="C73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1547,13 +1517,13 @@
       <c r="A74" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="4">
         <v>1002982.0</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="C74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1561,13 +1531,13 @@
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="4">
         <v>1003037.0</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="C75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1575,13 +1545,13 @@
       <c r="A76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="4">
         <v>1003039.0</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="2">
+      <c r="C76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1589,13 +1559,13 @@
       <c r="A77" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="4">
         <v>1003054.0</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="2">
+      <c r="C77" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1603,13 +1573,13 @@
       <c r="A78" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="4">
         <v>1003082.0</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="2">
+      <c r="C78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -1617,13 +1587,13 @@
       <c r="A79" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="4">
         <v>1003089.0</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="2">
+      <c r="C79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="4">
         <v>20.0</v>
       </c>
     </row>
@@ -1631,13 +1601,13 @@
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="4">
         <v>1003090.0</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="2">
+      <c r="C80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="4">
         <v>58.0</v>
       </c>
     </row>
@@ -1645,13 +1615,13 @@
       <c r="A81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="4">
         <v>1003135.0</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D81" s="2">
+      <c r="C81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="4">
         <v>10.0</v>
       </c>
     </row>
@@ -1659,13 +1629,13 @@
       <c r="A82" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="4">
         <v>1003139.0</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="2">
+      <c r="C82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -1673,13 +1643,13 @@
       <c r="A83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="4">
         <v>1007878.0</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="2">
+      <c r="C83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1687,13 +1657,13 @@
       <c r="A84" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="4">
         <v>5.0</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1701,13 +1671,13 @@
       <c r="A85" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="4">
         <v>3.0</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1715,13 +1685,13 @@
       <c r="A86" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="4">
         <v>1002331.0</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="2">
+      <c r="C86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1729,13 +1699,13 @@
       <c r="A87" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="4">
         <v>1002340.0</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="2">
+      <c r="C87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1743,13 +1713,13 @@
       <c r="A88" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="4">
         <v>1002341.0</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="C88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1757,13 +1727,13 @@
       <c r="A89" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="4">
         <v>1002349.0</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D89" s="2">
+      <c r="C89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1771,13 +1741,13 @@
       <c r="A90" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="4">
         <v>1002362.0</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="2">
+      <c r="C90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1785,13 +1755,13 @@
       <c r="A91" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="4">
         <v>1002364.0</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="2">
+      <c r="C91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1799,13 +1769,13 @@
       <c r="A92" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="4">
         <v>1002367.0</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="2">
+      <c r="C92" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1813,13 +1783,13 @@
       <c r="A93" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="4">
         <v>1002426.0</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="2">
+      <c r="C93" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1827,13 +1797,13 @@
       <c r="A94" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="4">
         <v>1002435.0</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="2">
+      <c r="C94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="4">
         <v>46.0</v>
       </c>
     </row>
@@ -1841,13 +1811,13 @@
       <c r="A95" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="4">
         <v>1002442.0</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="2">
+      <c r="C95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="4">
         <v>48.0</v>
       </c>
     </row>
@@ -1855,13 +1825,13 @@
       <c r="A96" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="4">
         <v>1002447.0</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="2">
+      <c r="C96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="4">
         <v>64.0</v>
       </c>
     </row>
@@ -1869,13 +1839,13 @@
       <c r="A97" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="4">
         <v>1002451.0</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97" s="2">
+      <c r="C97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="4">
         <v>14.0</v>
       </c>
     </row>
@@ -1883,13 +1853,13 @@
       <c r="A98" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="4">
         <v>1002458.0</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="2">
+      <c r="C98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1897,13 +1867,13 @@
       <c r="A99" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="4">
         <v>1002460.0</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="C99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="4">
         <v>86.0</v>
       </c>
     </row>
@@ -1911,13 +1881,13 @@
       <c r="A100" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="4">
         <v>1002465.0</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="2">
+      <c r="C100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="4">
         <v>12.0</v>
       </c>
     </row>
@@ -1925,13 +1895,13 @@
       <c r="A101" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="4">
         <v>1002469.0</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" s="2">
+      <c r="C101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -1939,13 +1909,13 @@
       <c r="A102" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="4">
         <v>1002471.0</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="2">
+      <c r="C102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -1953,13 +1923,13 @@
       <c r="A103" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="4">
         <v>1002472.0</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D103" s="2">
+      <c r="C103" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1967,13 +1937,13 @@
       <c r="A104" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="4">
         <v>1002508.0</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D104" s="2">
+      <c r="C104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -1981,13 +1951,13 @@
       <c r="A105" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="4">
         <v>1002509.0</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D105" s="2">
+      <c r="C105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -1995,13 +1965,13 @@
       <c r="A106" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="4">
         <v>1002511.0</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D106" s="2">
+      <c r="C106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -2009,13 +1979,13 @@
       <c r="A107" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="4">
         <v>1002563.0</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D107" s="2">
+      <c r="C107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2023,13 +1993,13 @@
       <c r="A108" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="4">
         <v>1002565.0</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D108" s="2">
+      <c r="C108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2037,13 +2007,13 @@
       <c r="A109" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="4">
         <v>1002571.0</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109" s="2">
+      <c r="C109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2051,13 +2021,13 @@
       <c r="A110" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="4">
         <v>1002673.0</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D110" s="2">
+      <c r="C110" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" s="4">
         <v>12.0</v>
       </c>
     </row>
@@ -2065,13 +2035,13 @@
       <c r="A111" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="4">
         <v>1002682.0</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D111" s="2">
+      <c r="C111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" s="4">
         <v>3.0</v>
       </c>
     </row>
@@ -2079,13 +2049,13 @@
       <c r="A112" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="4">
         <v>1002692.0</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="2">
+      <c r="C112" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -2093,13 +2063,13 @@
       <c r="A113" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="4">
         <v>1002693.0</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D113" s="2">
+      <c r="C113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -2107,13 +2077,13 @@
       <c r="A114" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="4">
         <v>1002712.0</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D114" s="2">
+      <c r="C114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -2121,13 +2091,13 @@
       <c r="A115" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="4">
         <v>1002716.0</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D115" s="2">
+      <c r="C115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2135,13 +2105,13 @@
       <c r="A116" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="4">
         <v>1002717.0</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D116" s="2">
+      <c r="C116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2149,13 +2119,13 @@
       <c r="A117" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="4">
         <v>1002800.0</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D117" s="2">
+      <c r="C117" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2163,13 +2133,13 @@
       <c r="A118" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="4">
         <v>1002808.0</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D118" s="2">
+      <c r="C118" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2177,13 +2147,13 @@
       <c r="A119" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="4">
         <v>1002848.0</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D119" s="2">
+      <c r="C119" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2191,13 +2161,13 @@
       <c r="A120" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="4">
         <v>1002873.0</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="2">
+      <c r="C120" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="4">
         <v>2.0</v>
       </c>
     </row>
@@ -2205,13 +2175,13 @@
       <c r="A121" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="4">
         <v>1002914.0</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" s="2">
+      <c r="C121" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2219,13 +2189,13 @@
       <c r="A122" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="4">
         <v>1002915.0</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D122" s="2">
+      <c r="C122" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2233,13 +2203,13 @@
       <c r="A123" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="4">
         <v>1002927.0</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D123" s="2">
+      <c r="C123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2247,13 +2217,13 @@
       <c r="A124" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="4">
         <v>1002937.0</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D124" s="2">
+      <c r="C124" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -2261,13 +2231,13 @@
       <c r="A125" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="4">
         <v>1002963.0</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D125" s="2">
+      <c r="C125" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2275,13 +2245,13 @@
       <c r="A126" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="4">
         <v>1002967.0</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D126" s="2">
+      <c r="C126" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2289,13 +2259,13 @@
       <c r="A127" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="4">
         <v>1002977.0</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D127" s="2">
+      <c r="C127" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2303,13 +2273,13 @@
       <c r="A128" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="4">
         <v>1002978.0</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D128" s="2">
+      <c r="C128" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2317,13 +2287,13 @@
       <c r="A129" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="4">
         <v>1003059.0</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D129" s="2">
+      <c r="C129" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="4">
         <v>4.0</v>
       </c>
     </row>
@@ -2331,13 +2301,13 @@
       <c r="A130" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="4">
         <v>1003067.0</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D130" s="2">
+      <c r="C130" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" s="4">
         <v>12.0</v>
       </c>
     </row>
@@ -2345,13 +2315,13 @@
       <c r="A131" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="4">
         <v>1003072.0</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D131" s="2">
+      <c r="C131" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" s="4">
         <v>32.0</v>
       </c>
     </row>
@@ -2359,13 +2329,13 @@
       <c r="A132" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="4">
         <v>1003076.0</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D132" s="2">
+      <c r="C132" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" s="4">
         <v>32.0</v>
       </c>
     </row>
@@ -2373,13 +2343,13 @@
       <c r="A133" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="4">
         <v>1003081.0</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D133" s="2">
+      <c r="C133" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -2387,13 +2357,13 @@
       <c r="A134" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="4">
         <v>1003085.0</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D134" s="2">
+      <c r="C134" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" s="4">
         <v>70.0</v>
       </c>
     </row>
@@ -2401,13 +2371,13 @@
       <c r="A135" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="4">
         <v>1003088.0</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D135" s="2">
+      <c r="C135" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -2415,13 +2385,13 @@
       <c r="A136" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="4">
         <v>1003090.0</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D136" s="2">
+      <c r="C136" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="4">
         <v>64.0</v>
       </c>
     </row>
@@ -2429,13 +2399,13 @@
       <c r="A137" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="4">
         <v>1003092.0</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D137" s="2">
+      <c r="C137" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" s="4">
         <v>88.0</v>
       </c>
     </row>
@@ -2443,13 +2413,13 @@
       <c r="A138" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="4">
         <v>1003138.0</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D138" s="2">
+      <c r="C138" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -2457,13 +2427,13 @@
       <c r="A139" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="4">
         <v>1003139.0</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D139" s="2">
+      <c r="C139" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" s="4">
         <v>32.0</v>
       </c>
     </row>
@@ -2471,13 +2441,13 @@
       <c r="A140" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="4">
         <v>1003169.0</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D140" s="2">
+      <c r="C140" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" s="4">
         <v>8.0</v>
       </c>
     </row>
@@ -2485,13 +2455,13 @@
       <c r="A141" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="4">
         <v>1007231.0</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="2">
+      <c r="C141" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" s="4">
         <v>32.0</v>
       </c>
     </row>
@@ -2499,13 +2469,13 @@
       <c r="A142" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="4">
         <v>1008482.0</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D142" s="2">
+      <c r="C142" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2513,13 +2483,13 @@
       <c r="A143" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="4">
         <v>5.0</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -2527,13 +2497,13 @@
       <c r="A144" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="4">
         <v>4.0</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="4">
         <v>6.0</v>
       </c>
     </row>
@@ -2541,13 +2511,13 @@
       <c r="A145" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="4">
         <v>2.0</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -3538,897 +3508,897 @@
       <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>1006343.0</v>
       </c>
-      <c r="D2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>7.0</v>
       </c>
-      <c r="D3" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>1007042.0</v>
       </c>
-      <c r="D4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>6.0</v>
       </c>
-      <c r="D5" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>1002603.0</v>
       </c>
-      <c r="D6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>1008481.0</v>
       </c>
-      <c r="D7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>1002399.0</v>
       </c>
-      <c r="D8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>1006786.0</v>
       </c>
-      <c r="D9" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>1002342.0</v>
       </c>
-      <c r="D10" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>1002681.0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="4">
         <v>4.0</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>1002702.0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="4">
         <v>22.0</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>1002702.0</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="4">
         <v>22.0</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>1002912.0</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="4">
         <v>16.0</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>1002913.0</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>32.0</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>1002919.0</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="4">
         <v>16.0</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>1002919.0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="4">
         <v>16.0</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>1007678.0</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="4">
         <v>32.0</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>1007678.0</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="4">
         <v>32.0</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <v>1007679.0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="4">
         <v>32.0</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>1007679.0</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="4">
         <v>32.0</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>1007681.0</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="4">
         <v>16.0</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="4">
         <v>1007681.0</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="4">
         <v>16.0</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="4">
         <v>1007682.0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="4">
         <v>32.0</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="4">
         <v>1007682.0</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>32.0</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="4">
         <v>1007684.0</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="4">
         <v>16.0</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="4">
         <v>1007684.0</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="4">
         <v>16.0</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="4">
         <v>1006342.0</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="4">
         <v>16.0</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="4">
         <v>1006374.0</v>
       </c>
-      <c r="D29" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>1002395.0</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="4">
         <v>64.0</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="4">
         <v>1002519.0</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="4">
         <v>12.0</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="4">
         <v>1002573.0</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="4">
         <v>16.0</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="4">
         <v>1002667.0</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="4">
         <v>20.0</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="4">
         <v>1002678.0</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="4">
         <v>16.0</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="4">
         <v>1002681.0</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="4">
         <v>4.0</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="4">
         <v>1002685.0</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="4">
         <v>2.0</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="4">
         <v>1002696.0</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="4">
         <v>64.0</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="4">
         <v>1002697.0</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="4">
         <v>16.0</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="4">
         <v>1002703.0</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="4">
         <v>8.0</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="4">
         <v>1002734.0</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="4">
         <v>4.0</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="4">
         <v>1002921.0</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="4">
         <v>128.0</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="4">
         <v>1002985.0</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="4">
         <v>32.0</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="4">
         <v>1002988.0</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="4">
         <v>32.0</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="4">
         <v>1003068.0</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="4">
         <v>12.0</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="4">
         <v>1003169.0</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="4">
         <v>16.0</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="4">
         <v>1007682.0</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="4">
         <v>32.0</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="4">
         <v>9.0</v>
       </c>
-      <c r="D47" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>1002398.0</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="4">
         <v>64.0</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="4">
         <v>9.0</v>
       </c>
-      <c r="D49" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="4">
         <v>1002410.0</v>
       </c>
-      <c r="D50" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="4">
         <v>1006353.0</v>
       </c>
-      <c r="D51" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="4">
         <v>1007952.0</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="4">
         <v>4.0</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="4">
         <v>1003154.0</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="4">
         <v>4.0</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5398,46 +5368,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>2000.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>2.0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>10000.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>1000.0</v>
       </c>
     </row>
@@ -6442,112 +6412,112 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>2000.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>2.0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>2000.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>2000.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>4.0</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>300.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>5.0</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>2200.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>6.0</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>24000.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>7.0</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>32500.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>8.0</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>20000.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>9.0</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>10100.0</v>
       </c>
     </row>
